--- a/Coca Cola - DCF Valuation/CocaCola_DCF_Valuation.xlsx
+++ b/Coca Cola - DCF Valuation/CocaCola_DCF_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Môj PC\Desktop\Coca Cola - DCF Valuation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1831A2CB-B216-494B-9473-79C01965B792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFA0B340-C739-49DF-8AFF-582395007FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F236B8D2-2DE0-418F-A62D-0782908C1CB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{F236B8D2-2DE0-418F-A62D-0782908C1CB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -989,7 +989,7 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1085,7 +1085,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1123,6 +1122,8 @@
     <xf numFmtId="2" fontId="17" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -2920,8 +2921,8 @@
         <v>80</v>
       </c>
       <c r="C26" s="60">
-        <f>(C22*C9)+(C23*C15)</f>
-        <v>6.8500000000000005E-2</v>
+        <f>(C22*C9)+(C23*C15)*(1-C14)</f>
+        <v>6.6728999999999997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3009,23 +3010,23 @@
       </c>
       <c r="C7" s="43">
         <f>1/(1+WACC!$C$26)</f>
-        <v>0.93589143659335516</v>
+        <v>0.93744521804507042</v>
       </c>
       <c r="D7" s="43">
         <f>C7/(1+WACC!$C$26)</f>
-        <v>0.87589278108877411</v>
+        <v>0.87880353683556967</v>
       </c>
       <c r="E7" s="43">
         <f>D7/(1+WACC!$C$26)</f>
-        <v>0.81974055319492189</v>
+        <v>0.82383017320759966</v>
       </c>
       <c r="F7" s="43">
         <f>E7/(1+WACC!$C$26)</f>
-        <v>0.76718816396342715</v>
+        <v>0.77229565635470643</v>
       </c>
       <c r="G7" s="43">
         <f>F7/(1+WACC!$C$26)</f>
-        <v>0.71800483290915029</v>
+        <v>0.72398486996669853</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3034,23 +3035,23 @@
       </c>
       <c r="C8" s="64">
         <f>C6*C7</f>
-        <v>9127.1408366869455</v>
+        <v>9142.2938572027197</v>
       </c>
       <c r="D8" s="64">
         <f t="shared" ref="D8:G8" si="1">D6*D7</f>
-        <v>8883.6934676222972</v>
+        <v>8913.2156447334146</v>
       </c>
       <c r="E8" s="64">
         <f t="shared" si="1"/>
-        <v>8646.7395473347569</v>
+        <v>8689.8774389022419</v>
       </c>
       <c r="F8" s="64">
         <f t="shared" si="1"/>
-        <v>8416.1058766758524</v>
+        <v>8472.1354125165162</v>
       </c>
       <c r="G8" s="64">
         <f t="shared" si="1"/>
-        <v>8191.6238762216999</v>
+        <v>8259.8493422576648</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3082,7 +3083,7 @@
       </c>
       <c r="C13" s="48">
         <f>G6*(1+'DCF &amp; Sensitivity'!$J$10)/('DCF &amp; Sensitivity'!$J$9-'DCF &amp; Sensitivity'!$J$10)</f>
-        <v>268829.69796829246</v>
+        <v>280238.96718399011</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3091,13 +3092,13 @@
       </c>
       <c r="C14" s="48">
         <f>C13/(1+WACC!C26)^5</f>
-        <v>193021.02237074121</v>
+        <v>202888.77221630301</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -3109,47 +3110,47 @@
       <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="67">
+      <c r="C18" s="97">
         <f>SUM(C8:G8)+C14</f>
-        <v>236286.32597528276</v>
-      </c>
-      <c r="D18" s="96"/>
+        <v>246366.14391191557</v>
+      </c>
+      <c r="D18" s="95"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="67">
+      <c r="C19" s="97">
         <v>30069</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="67">
+      <c r="C20" s="97">
         <f>C18-C19</f>
-        <v>206217.32597528276</v>
+        <v>216297.14391191557</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="96" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="67">
+      <c r="C21" s="97">
         <v>7040</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="68">
+      <c r="C22" s="67">
         <f>C20/C21</f>
-        <v>29.292233803307209</v>
+        <v>30.724026123851644</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3230,7 +3231,7 @@
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="66"/>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="77" t="s">
         <v>94</v>
       </c>
       <c r="D5" s="66"/>
@@ -3253,7 +3254,7 @@
       <c r="A7" s="66"/>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="80" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="66"/>
@@ -3262,149 +3263,149 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="66"/>
-      <c r="B8" s="80">
+      <c r="B8" s="79">
         <f>'Free Cash Flow'!C22</f>
-        <v>29.292233803307209</v>
-      </c>
-      <c r="C8" s="73">
+        <v>30.724026123851644</v>
+      </c>
+      <c r="C8" s="72">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="73">
         <v>0.02</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="74">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F8" s="74">
+      <c r="F8" s="73">
         <v>0.03</v>
       </c>
-      <c r="G8" s="76">
+      <c r="G8" s="75">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I8" s="82" t="s">
+      <c r="I8" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="83"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="66"/>
-      <c r="B9" s="70">
+      <c r="B9" s="69">
         <v>0.06</v>
       </c>
-      <c r="C9" s="88">
+      <c r="C9" s="87">
         <f t="dataTable" ref="C9:G13" dt2D="1" dtr="1" r1="J10" r2="J9"/>
-        <v>28.119734521999359</v>
-      </c>
-      <c r="D9" s="88">
-        <v>31.545839836391327</v>
-      </c>
-      <c r="E9" s="89">
-        <v>35.950832383466711</v>
-      </c>
-      <c r="F9" s="88">
-        <v>41.824155779567228</v>
-      </c>
-      <c r="G9" s="90">
-        <v>50.04680853410796</v>
-      </c>
-      <c r="I9" s="84" t="s">
+        <v>28.368446365827324</v>
+      </c>
+      <c r="D9" s="87">
+        <v>31.823086636815781</v>
+      </c>
+      <c r="E9" s="88">
+        <v>36.264766985229492</v>
+      </c>
+      <c r="F9" s="87">
+        <v>42.18700744978112</v>
+      </c>
+      <c r="G9" s="89">
+        <v>50.478144100153415</v>
+      </c>
+      <c r="I9" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="85">
+      <c r="J9" s="84">
         <f>WACC!C26</f>
-        <v>6.8500000000000005E-2</v>
+        <v>6.6728999999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66"/>
-      <c r="B10" s="71">
+      <c r="B10" s="70">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="C10" s="88">
-        <v>25.495208564182111</v>
-      </c>
-      <c r="D10" s="88">
-        <v>28.249021514995285</v>
-      </c>
-      <c r="E10" s="89">
-        <v>31.691287703511737</v>
-      </c>
-      <c r="F10" s="88">
-        <v>36.117058517318604</v>
-      </c>
-      <c r="G10" s="90">
-        <v>42.018086269061115</v>
-      </c>
-      <c r="I10" s="86" t="s">
+      <c r="C10" s="87">
+        <v>25.722061554466357</v>
+      </c>
+      <c r="D10" s="87">
+        <v>28.49881014963821</v>
+      </c>
+      <c r="E10" s="88">
+        <v>31.969745893603019</v>
+      </c>
+      <c r="F10" s="87">
+        <v>36.432377564414914</v>
+      </c>
+      <c r="G10" s="89">
+        <v>42.382553125497452</v>
+      </c>
+      <c r="I10" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="87">
+      <c r="J10" s="86">
         <f>'Free Cash Flow'!C12</f>
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="79"/>
-      <c r="B11" s="77">
-        <v>6.8500000000000005E-2</v>
-      </c>
-      <c r="C11" s="89">
-        <v>23.949926925467285</v>
-      </c>
-      <c r="D11" s="89">
-        <v>26.345703721199627</v>
-      </c>
-      <c r="E11" s="89">
-        <v>29.292233803307209</v>
-      </c>
-      <c r="F11" s="89">
-        <v>33.004096374273914</v>
-      </c>
-      <c r="G11" s="91">
-        <v>37.823977623141118</v>
+      <c r="A11" s="78"/>
+      <c r="B11" s="76">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="C11" s="88">
+        <v>24.938895449750255</v>
+      </c>
+      <c r="D11" s="88">
+        <v>27.530712500267448</v>
+      </c>
+      <c r="E11" s="88">
+        <v>30.744068411819924</v>
+      </c>
+      <c r="F11" s="88">
+        <v>34.832998141234121</v>
+      </c>
+      <c r="G11" s="90">
+        <v>40.211811066047126</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="66"/>
-      <c r="B12" s="71">
+      <c r="B12" s="70">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C12" s="88">
-        <v>21.558419627456249</v>
-      </c>
-      <c r="D12" s="88">
-        <v>23.453649411146493</v>
-      </c>
-      <c r="E12" s="89">
-        <v>25.727925151574777</v>
-      </c>
-      <c r="F12" s="88">
-        <v>28.507595500987129</v>
-      </c>
-      <c r="G12" s="90">
-        <v>31.982183437752568</v>
+      <c r="C12" s="87">
+        <v>21.752484337424914</v>
+      </c>
+      <c r="D12" s="87">
+        <v>23.663498895561759</v>
+      </c>
+      <c r="E12" s="88">
+        <v>25.956716365325953</v>
+      </c>
+      <c r="F12" s="87">
+        <v>28.759537717259978</v>
+      </c>
+      <c r="G12" s="89">
+        <v>32.263064407177517</v>
       </c>
       <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="66"/>
-      <c r="B13" s="72">
+      <c r="B13" s="71">
         <v>0.08</v>
       </c>
-      <c r="C13" s="92">
-        <v>20.044270036407841</v>
-      </c>
-      <c r="D13" s="93">
-        <v>21.655384872203193</v>
-      </c>
-      <c r="E13" s="94">
-        <v>23.55942967814315</v>
-      </c>
-      <c r="F13" s="93">
-        <v>25.844283445271106</v>
-      </c>
-      <c r="G13" s="95">
-        <v>28.636882493983048</v>
+      <c r="C13" s="91">
+        <v>20.225723869332054</v>
+      </c>
+      <c r="D13" s="92">
+        <v>21.850257175283083</v>
+      </c>
+      <c r="E13" s="93">
+        <v>23.7701601732252</v>
+      </c>
+      <c r="F13" s="92">
+        <v>26.07404377075575</v>
+      </c>
+      <c r="G13" s="94">
+        <v>28.889901501070863</v>
       </c>
       <c r="H13" s="66"/>
     </row>
@@ -3636,15 +3637,15 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F334DA6-6AE1-4483-BFAA-F9FAA53EF735}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="3091b951-ef1e-4cf5-aa2d-a140000e2f2a"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
